--- a/data/grants.xlsx
+++ b/data/grants.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://khazanahcommy-my.sharepoint.com/personal/khalis_khalid_khazanah_com_my/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alifhakimiazwan/Codes/msfd-web/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DB46AD1-4E9F-4C24-B5E1-2522D184CF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EA30CA-E73C-1447-A74D-A4B462DFA5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-80" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Financing Directory" sheetId="1" r:id="rId1"/>
     <sheet name="Key &amp; Definitions" sheetId="2" r:id="rId2"/>
+    <sheet name="Valid Values" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -44,28 +45,151 @@
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>System</author>
+  </authors>
+  <commentList>
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>FILTER COLUMN — Use comma-separated values from the 'Valid Values' sheet.
+E.g.: Grant, Soft Loan</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Display text shown on the website card — preserve the original descriptive label (e.g. 'Grant — Outright (Non-Reimbursable)'). Do not change this format.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>FILTER COLUMN — Enter numeric RM amount as an integer (e.g. 50000). Leave blank if not applicable.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Optional qualifier text (e.g. 'estimated', 'per SME', 'Fund-level only'). Leave blank if none.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>FILTER COLUMN — Enter numeric RM amount as an integer (e.g. 5000000). Leave blank if not applicable.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Optional qualifier text. Leave blank if none.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>FILTER COLUMN — Use comma-separated values from the 'Valid Values' sheet.
+E.g.: IC Design &amp; Embedded Systems, Advanced Packaging / OSAT</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>FILTER COLUMN — Use comma-separated values from the 'Valid Values' sheet.
+E.g.: SME (revenue-generating), Growth-stage</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>FILTER COLUMN — Use comma-separated values from the 'Valid Values' sheet.
+E.g.: R&amp;D &amp; Prototyping, CapEx</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="524">
   <si>
     <t>MALAYSIA SEMICONDUCTOR INDUSTRY — FINANCING SOURCES DIRECTORY</t>
   </si>
@@ -100,16 +224,30 @@
     <t>Type of Financing</t>
   </si>
   <si>
+    <t>Financing
+Type Notes</t>
+  </si>
+  <si>
     <t>Website / Application Link</t>
   </si>
   <si>
     <t>Total Pool / Mandate</t>
   </si>
   <si>
-    <t>Typical Ticket Size (Min)</t>
-  </si>
-  <si>
-    <t>Typical Ticket Size (Max)</t>
+    <t>Ticket Min
+(RM)</t>
+  </si>
+  <si>
+    <t>Ticket Min
+Notes</t>
+  </si>
+  <si>
+    <t>Ticket Max
+(RM)</t>
+  </si>
+  <si>
+    <t>Ticket Max
+Notes</t>
   </si>
   <si>
     <t>Cost of Capital</t>
@@ -154,6 +292,9 @@
     <t>NSS Capital Grant — Ministry of Finance / MITI</t>
   </si>
   <si>
+    <t>Grant</t>
+  </si>
+  <si>
     <t>Grant — Outright (Non-Reimbursable)</t>
   </si>
   <si>
@@ -181,23 +322,16 @@
     <t>Both (conventional &amp; Islamic channels available)</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Fabrication / Foundry
-Advanced Packaging / OSAT
-Equipment Manufacturing
-Advanced Materials</t>
+    <t>IC Design &amp; Embedded Systems, Fabrication / Foundry, Advanced Packaging / OSAT, Equipment Manufacturing, Advanced Materials</t>
   </si>
   <si>
     <t>Malaysian-incorporated entity; domestic investment preferred; foreign JV with Malaysian partner considered</t>
   </si>
   <si>
-    <t>Growth-stage to established; typically &gt;RM5M revenue or strategic greenfield investment</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-CapEx (Factory, Equipment)
-Talent Acquisition &amp; Upskilling
-Infrastructure</t>
+    <t>Growth-stage, Established</t>
+  </si>
+  <si>
+    <t>R&amp;D &amp; Prototyping, CapEx, Talent Acquisition, M&amp;A</t>
   </si>
   <si>
     <t>None (grant); KPI milestones, audit, outcome reporting required</t>
@@ -224,10 +358,10 @@
     <t>RM200 million</t>
   </si>
   <si>
-    <t>RM100,000 (estimated)</t>
-  </si>
-  <si>
-    <t>RM5 million (estimated; details TBC)</t>
+    <t>estimated</t>
+  </si>
+  <si>
+    <t>estimated; details TBC</t>
   </si>
   <si>
     <t>0% — matching grant; recipient must co-invest equal amount</t>
@@ -239,20 +373,13 @@
     <t>Both</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Advanced Packaging / OSAT
-Equipment Manufacturing</t>
+    <t>IC Design &amp; Embedded Systems, Advanced Packaging / OSAT, Equipment Manufacturing</t>
   </si>
   <si>
     <t>Malaysian SME; ≥51% Malaysian-owned; must co-invest via Khazanah/KWAP channel</t>
   </si>
   <si>
-    <t>SME (revenue &lt;RM50M or &lt;200 employees); operating business</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-CapEx
-Talent Acquisition</t>
+    <t>SME (revenue-generating)</t>
   </si>
   <si>
     <t>None; business plan, co-investment proof &amp; outcome reporting</t>
@@ -279,9 +406,6 @@
     <t>RM180 million</t>
   </si>
   <si>
-    <t>RM5 million (estimated)</t>
-  </si>
-  <si>
     <t>0% grant; soft loan component subsidised (rate TBC)</t>
   </si>
   <si>
@@ -294,12 +418,10 @@
     <t>Malaysian SMEs and mid-tier companies; ≥51% Malaysian equity</t>
   </si>
   <si>
-    <t>SME to mid-tier; operating business aligned with NIMP 2030 sectors</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-CapEx
-OpEx / Working Capital</t>
+    <t>SME (revenue-generating), Established</t>
+  </si>
+  <si>
+    <t>R&amp;D &amp; Prototyping, CapEx, OpEx / Working Capital</t>
   </si>
   <si>
     <t>None for grant; project alignment with NIMP 2030 sectors required</t>
@@ -317,16 +439,19 @@
     <t>Strategic Co-Investment Fund (CoSIF) — MOF / SC Malaysia</t>
   </si>
   <si>
+    <t>Grant, Crowdfunding</t>
+  </si>
+  <si>
     <t>Grant — Matching (Co-Investment via ECF/P2P)</t>
   </si>
   <si>
     <t>https://www.sc.com.my</t>
   </si>
   <si>
-    <t>RM50,000 (based on min ECF raise)</t>
-  </si>
-  <si>
-    <t>RM5 million (matching cap estimated; ECF platform limit ~RM5M)</t>
+    <t>based on min ECF raise</t>
+  </si>
+  <si>
+    <t>matching cap estimated; ECF platform limit ~</t>
   </si>
   <si>
     <t>0% grant match; underlying ECF = equity dilution; P2P = 5%–15% p.a.</t>
@@ -341,21 +466,10 @@
     <t>Both (platform-dependent)</t>
   </si>
   <si>
-    <t>Advanced Packaging / OSAT
-Equipment Manufacturing
-IC Design (via ECF-backed startups)</t>
-  </si>
-  <si>
     <t>Malaysian SMEs and mid-tier companies; ≥51% Malaysian-owned; must raise on SC-licensed ECF/P2P platform first</t>
   </si>
   <si>
-    <t>SME to mid-tier; any stage that can raise on ECF/P2P platform</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-CapEx
-OpEx / Working Capital
-Export Promotion</t>
+    <t>R&amp;D &amp; Prototyping, CapEx, OpEx / Working Capital, Export Promotion</t>
   </si>
   <si>
     <t>None for grant; ECF/P2P platform requirements apply for underlying raise</t>
@@ -379,32 +493,22 @@
     <t>Ongoing rolling programme (RM1B+ deployed since 2003)</t>
   </si>
   <si>
-    <t>RM50,000</t>
-  </si>
-  <si>
-    <t>RM150,000</t>
-  </si>
-  <si>
     <t>Up to 18 months</t>
   </si>
   <si>
     <t>Both (technology-neutral)</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Advanced Materials &amp; Substrates
-Equipment Manufacturing (sensors, photonics)</t>
+    <t>IC Design &amp; Embedded Systems, Equipment Manufacturing, Advanced Materials</t>
   </si>
   <si>
     <t>Malaysian-incorporated; majority (&gt;50%) Malaysian-owned and managed</t>
   </si>
   <si>
-    <t>Pre-revenue to early revenue; technology-based startup; &lt;5 years operating preferred</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-Prototype development &amp; validation
-IP filing</t>
+    <t>Pre-revenue, SME (revenue-generating)</t>
+  </si>
+  <si>
+    <t>R&amp;D &amp; Prototyping</t>
   </si>
   <si>
     <t>None; IP assignment to Malaysian entity; milestone reporting</t>
@@ -422,38 +526,28 @@
     <t>Cradle Fund — Equity Investment Programme (Budget 2026)</t>
   </si>
   <si>
+    <t>Grant, Equity</t>
+  </si>
+  <si>
     <t>Equity / Grant Hybrid</t>
   </si>
   <si>
     <t>RM55 million (Budget 2026 allocation)</t>
   </si>
   <si>
-    <t>RM500,000</t>
-  </si>
-  <si>
-    <t>RM5 million</t>
-  </si>
-  <si>
     <t>Grant portion: 0%; Equity portion: Cradle takes minority stake (est. 10%–20%)</t>
   </si>
   <si>
     <t>Equity: 5–7 years to exit; grant: project-based</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Advanced Materials
-Equipment Manufacturing (deep-tech hardware)</t>
-  </si>
-  <si>
     <t>Malaysian-incorporated; majority Malaysian-owned</t>
   </si>
   <si>
-    <t>Early-stage startup; pre-Series A; scalable tech business model</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-Product development
-Go-to-market</t>
+    <t>Early-stage (Seed–Series A)</t>
+  </si>
+  <si>
+    <t>R&amp;D &amp; Prototyping, Go-to-market</t>
   </si>
   <si>
     <t>None for grant; equity dilution for founders (Cradle minority stake)</t>
@@ -474,6 +568,9 @@
     <t>BPMB — Semiconductor Financing Programme (NSS-linked)</t>
   </si>
   <si>
+    <t>Soft Loan</t>
+  </si>
+  <si>
     <t>Soft Loan — Subsidised (Islamic: Tawarruq)</t>
   </si>
   <si>
@@ -483,7 +580,7 @@
     <t>RM500 million</t>
   </si>
   <si>
-    <t>RM100 million (above RM100M case-by-case)</t>
+    <t>above  case-by-case</t>
   </si>
   <si>
     <t>Subsidised profit rate below market; Govt pays interest subsidy; indicatively 3%–5% p.a. (exact rate not published; varies by project risk)</t>
@@ -498,21 +595,13 @@
     <t>Yes — Shariah-compliant (Tawarruq structure); Bank Negara's Shariah Advisory Council oversight</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Fabrication / Foundry
-Advanced Packaging / OSAT
-Equipment Manufacturing</t>
+    <t>IC Design &amp; Embedded Systems, Fabrication / Foundry, Advanced Packaging / OSAT, Equipment Manufacturing</t>
   </si>
   <si>
     <t>≥51% Malaysian-owned; Private Limited, Public Company or Co-operative; incorporated in Malaysia</t>
   </si>
   <si>
-    <t>Growth-stage to established; not pre-revenue for large loans; &gt;RM5M revenue or project bankability required</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-CapEx (Machinery, Equipment, Land/Factory)
-OpEx / Working Capital</t>
+    <t>Pre-revenue, Growth-stage, Established</t>
   </si>
   <si>
     <t>Fixed assets (land, factory, machinery, equipment); personal or corporate guarantee; may require project account</t>
@@ -533,12 +622,6 @@
     <t>RM300 million</t>
   </si>
   <si>
-    <t>RM1 million</t>
-  </si>
-  <si>
-    <t>RM50 million</t>
-  </si>
-  <si>
     <t>Subsidised profit rate; indicatively 3%–5% p.a. (Govt subsidy applies)</t>
   </si>
   <si>
@@ -551,19 +634,13 @@
     <t>Yes — Shariah-compliant (Tawarruq)</t>
   </si>
   <si>
-    <t>Advanced Packaging / OSAT
-Equipment Manufacturing / Automation
-Fabrication (automation upgrades)</t>
+    <t>Fabrication / Foundry, Advanced Packaging / OSAT, Equipment Manufacturing</t>
   </si>
   <si>
     <t>≥51% Malaysian-owned; incorporated in Malaysia; Private Limited or Public Company</t>
   </si>
   <si>
-    <t>Operating SME to mid-tier; &gt;3 years operating history preferred; revenue-generating</t>
-  </si>
-  <si>
-    <t>CapEx (Machinery, Equipment, Automation systems)
-OpEx / Working Capital (limited)</t>
+    <t>CapEx, OpEx / Working Capital</t>
   </si>
   <si>
     <t>Fixed assets, equipment; corporate guarantee</t>
@@ -590,7 +667,7 @@
     <t>RM3.8B total (ADF + HTG combined, Budget 2025)</t>
   </si>
   <si>
-    <t>RM3 million per SME</t>
+    <t>per SME</t>
   </si>
   <si>
     <t>Up to 4% p.a. fixed (inclusive of SJPP guarantee fee); subsidised below market</t>
@@ -605,19 +682,13 @@
     <t>Both (Islamic version available at Islamic banks)</t>
   </si>
   <si>
-    <t>Advanced Packaging / OSAT
-Equipment Manufacturing / Automation
-Advanced Materials (digital-adjacent)</t>
+    <t>Advanced Packaging / OSAT, Equipment Manufacturing, Advanced Materials</t>
   </si>
   <si>
     <t>≥51% Malaysian-owned; SME definition per SME Corp; shareholders' funds ≤RM5M; PLC/GLC shareholding ≤20%</t>
   </si>
   <si>
-    <t>Operating SME; any sector; no revenue floor but must demonstrate repayment capacity</t>
-  </si>
-  <si>
-    <t>CapEx (Machinery, Equipment, Computer hardware/software, IT solutions)
-Tech support services &amp; intangible assets</t>
+    <t>CapEx</t>
   </si>
   <si>
     <t>SJPP government guarantee up to 90% of loan amount (no physical collateral needed for guaranteed portion)</t>
@@ -638,10 +709,7 @@
     <t>Part of RM3.8B BNM envelope (Budget 2025)</t>
   </si>
   <si>
-    <t>RM100,000</t>
-  </si>
-  <si>
-    <t>RM10 million per company</t>
+    <t>per company</t>
   </si>
   <si>
     <t>Up to 5% p.a. (inclusive of guarantee fee); 3.5% p.a. without guarantee</t>
@@ -650,22 +718,12 @@
     <t>6 months moratorium (optional)</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Advanced Packaging / OSAT
-Advanced Materials &amp; Substrates</t>
+    <t>IC Design &amp; Embedded Systems, Advanced Packaging / OSAT, Advanced Materials</t>
   </si>
   <si>
     <t>Malaysian SME or innovative startup; ≥51% Malaysian-owned; shareholders' funds ≤RM5M</t>
   </si>
   <si>
-    <t>SME or innovative startup; pre-revenue startups may qualify (digital tech, green tech, biotech focus)</t>
-  </si>
-  <si>
-    <t>CapEx (equipment, plant)
-OpEx / Working Capital
-R&amp;D (tech &amp; green activities)</t>
-  </si>
-  <si>
     <t>CGC or SJPP guarantee available; physical collateral may be waived with guarantee</t>
   </si>
   <si>
@@ -684,6 +742,9 @@
     <t>Khazanah — Dana Impak: Semiconductor &amp; Advanced Mfg</t>
   </si>
   <si>
+    <t>Equity</t>
+  </si>
+  <si>
     <t>Equity / Private Equity (Strategic Investment)</t>
   </si>
   <si>
@@ -693,12 +754,6 @@
     <t>RM1 billion mandate (semiconductor &amp; advanced manufacturing)</t>
   </si>
   <si>
-    <t>RM20 million</t>
-  </si>
-  <si>
-    <t>RM200 million+</t>
-  </si>
-  <si>
     <t>Equity returns expected; no fixed rate — market-rate or concessional PE IRR (target 8%–15% IRR typical for strategic Malaysian PE)</t>
   </si>
   <si>
@@ -714,15 +769,6 @@
     <t>Malaysian-incorporated entity; Khazanah-aligned strategic purpose; foreign partnerships considered under NSS</t>
   </si>
   <si>
-    <t>Mid-tier to growth-stage; typically revenue-generating (&gt;RM50M revenue); established operations</t>
-  </si>
-  <si>
-    <t>CapEx (Factory, Equipment)
-R&amp;D &amp; Prototyping
-Talent &amp; Ecosystem Building
-M&amp;A / Strategic Acquisitions</t>
-  </si>
-  <si>
     <t>None (equity); board representation; governance &amp; reporting commitments; co-investment with strategic partners</t>
   </si>
   <si>
@@ -744,30 +790,12 @@
     <t>RM550 million (joint)</t>
   </si>
   <si>
-    <t>RM10 million</t>
-  </si>
-  <si>
     <t>Equity returns; no fixed cost to recipient — dilution-based; strategic IRR target</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Advanced Packaging / OSAT
-Equipment Manufacturing
-Fabrication</t>
-  </si>
-  <si>
     <t>Malaysian companies partnering with MNCs under NSS; ≥30% Malaysian equity preferred</t>
   </si>
   <si>
-    <t>Growth-stage to established; companies that can co-invest or attract MNC anchor</t>
-  </si>
-  <si>
-    <t>CapEx
-R&amp;D &amp; Prototyping
-Talent Acquisition
-Ecosystem development</t>
-  </si>
-  <si>
     <t>None (equity); strategic partnership commitments with MNCs</t>
   </si>
   <si>
@@ -807,22 +835,13 @@
     <t>Both (KWAP invests via LP agreement; structure depends on GP)</t>
   </si>
   <si>
-    <t>IC Design
-Advanced Packaging / OSAT
-Equipment Manufacturing
-Energy transition &amp; digital (adjacent)</t>
-  </si>
-  <si>
     <t>Co-GP: international fund manager must partner with Malaysian GP; no direct SME eligibility</t>
   </si>
   <si>
-    <t>Growth-stage companies (via GP selection); GP must have institutional track record</t>
-  </si>
-  <si>
-    <t>CapEx
-R&amp;D
-M&amp;A
-Growth capital (as determined by GP mandate)</t>
+    <t>Growth-stage</t>
+  </si>
+  <si>
+    <t>R&amp;D &amp; Prototyping, CapEx, M&amp;A</t>
   </si>
   <si>
     <t>None (LP/GP equity structure); GP due diligence and investment mandate compliance</t>
@@ -840,16 +859,19 @@
     <t>KWAP — Dana Perintis (VC Early-Stage Fund)</t>
   </si>
   <si>
+    <t>Venture Capital</t>
+  </si>
+  <si>
     <t>Venture Capital (Direct + Fund of Funds)</t>
   </si>
   <si>
     <t>RM500 million (combined with Jelawang at RM750M post Budget 2026)</t>
   </si>
   <si>
-    <t>RM500,000 (direct startup investment)</t>
-  </si>
-  <si>
-    <t>RM20 million (via VC fund or direct)</t>
+    <t>direct startup investment</t>
+  </si>
+  <si>
+    <t>via VC fund or direct</t>
   </si>
   <si>
     <t>VC-style equity returns; no fixed cost to startup — dilution; KWAP targets portfolio-level IRR of 15%+</t>
@@ -858,21 +880,13 @@
     <t>7–10 years (venture investment horizon)</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Advanced Materials
-Equipment Manufacturing (deep-tech)</t>
-  </si>
-  <si>
     <t>Malaysian startup or Malaysian-incorporated entity; majority Malaysian-founded preferred</t>
   </si>
   <si>
-    <t>Pre-revenue to early revenue (Seed to Series A); high-growth scalable tech</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-Product Development
-Go-to-market
-Talent</t>
+    <t>Pre-revenue, Early-stage (Seed–Series A)</t>
+  </si>
+  <si>
+    <t>R&amp;D &amp; Prototyping, Talent Acquisition, Go-to-market</t>
   </si>
   <si>
     <t>None (equity); KWAP minority stake; founder dilution applies</t>
@@ -917,10 +931,7 @@
     <t>VC fund managers (GPs) — not direct startup applications; local emerging or regional GPs</t>
   </si>
   <si>
-    <t>VC fund managers with institutional track record; early-stage to growth-stage focus</t>
-  </si>
-  <si>
-    <t>Portfolio company-level: R&amp;D, product development, market expansion, talent</t>
+    <t>Early-stage (Seed–Series A), Growth-stage</t>
   </si>
   <si>
     <t>None for NFOF (LP agreement); GPs conduct own due diligence on portfolio companies</t>
@@ -944,31 +955,19 @@
     <t>RM250 million</t>
   </si>
   <si>
-    <t>RM100 million</t>
-  </si>
-  <si>
     <t>Equity returns; market-rate or strategic PE; Khazanah minority stake; IRR target 10%–15%</t>
   </si>
   <si>
     <t>5–7 years</t>
   </si>
   <si>
-    <t>Advanced Packaging / OSAT
-Equipment Manufacturing
-IC Design
-Advanced Materials</t>
+    <t>IC Design &amp; Embedded Systems, Advanced Packaging / OSAT, Equipment Manufacturing, Advanced Materials</t>
   </si>
   <si>
     <t>Malaysian mid-tier companies; ≥51% Malaysian equity; locally incorporated</t>
   </si>
   <si>
-    <t>Revenue RM50M–RM500M; established operations (&gt;5 years); profitable or near-profitable</t>
-  </si>
-  <si>
-    <t>CapEx
-R&amp;D
-M&amp;A / Internationalisation
-Talent &amp; Governance</t>
+    <t>Established</t>
   </si>
   <si>
     <t>None (equity); governance upgrade commitments; Khazanah board representation</t>
@@ -989,6 +988,9 @@
     <t>MTDC — SemiconStart Malaysia (with Silicon Catalyst UK)</t>
   </si>
   <si>
+    <t>Grant, Incubator / Accelerator</t>
+  </si>
+  <si>
     <t>Incubator / Accelerator Programme (Grant + In-Kind)</t>
   </si>
   <si>
@@ -1001,7 +1003,7 @@
     <t>Non-cash: discounted foundry access, mentorship, network (value est. RM200K–RM1M per company)</t>
   </si>
   <si>
-    <t>Cash grant component: est. RM500K–RM2M per company (TBC)</t>
+    <t>Cash grant component: est. – per company (TBC</t>
   </si>
   <si>
     <t>Grant portion: 0%; any equity: negotiated (MTDC may take convertible note)</t>
@@ -1010,21 +1012,10 @@
     <t>Cohort-based: 12–18 months per cohort</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Advanced Materials &amp; Substrates
-Equipment Manufacturing (sensors, photonics, MEMS, quantum)</t>
-  </si>
-  <si>
     <t>Malaysian-incorporated preferred; ≥51% Malaysian equity preferred; foreign startups with Malaysian subsidiary considered</t>
   </si>
   <si>
-    <t>TRL 4–commercial ready; pre-revenue to early revenue; semiconductor-focused startup</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-Foundry access (discounted multi-project wafer)
-Prototype creation
-Go-to-market support</t>
+    <t>Pre-revenue</t>
   </si>
   <si>
     <t>None; IP agreement with MTDC; programme participation commitments</t>
@@ -1051,10 +1042,10 @@
     <t>Single-site: RM250K (full grant); Multi-site: RM500K (70% grant); Commercialisation: RM4M (hybrid); Matching fund: RM15M</t>
   </si>
   <si>
-    <t>RM250,000 (single-site sandbox)</t>
-  </si>
-  <si>
-    <t>RM15 million (matching fund with investors/corporates)</t>
+    <t>single-site sandbox</t>
+  </si>
+  <si>
+    <t>matching fund with investors/corporates</t>
   </si>
   <si>
     <t>Grant: 0%; Convertible note portion: conversion at agreed valuation (typically 10%–20% discount to next round)</t>
@@ -1066,22 +1057,13 @@
     <t>N/A for grant; convertible note: converts at next funding round</t>
   </si>
   <si>
-    <t>Equipment Manufacturing / Automation
-Advanced Materials &amp; Substrates
-IC Design (software/EDA tools)
-Fabrication (process innovation)</t>
+    <t>IC Design &amp; Embedded Systems, Fabrication / Foundry, Equipment Manufacturing, Advanced Materials</t>
   </si>
   <si>
     <t>Malaysian individuals or Malaysian-owned companies; ≥51% Malaysian-owned</t>
   </si>
   <si>
-    <t>Pre-revenue to early revenue; technology readiness level TRL 4–7; must have testable product/service</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-Sandbox testing &amp; validation
-Commercialization
-CapEx (prototype equipment)</t>
+    <t>R&amp;D &amp; Prototyping, CapEx, Go-to-market</t>
   </si>
   <si>
     <t>None for grant; convertible note converts to equity; IP registered in Malaysia preferred</t>
@@ -1108,10 +1090,10 @@
     <t>Programme budget not disclosed; rolling allocation</t>
   </si>
   <si>
-    <t>RM50,000 (50% of RM100K min project)</t>
-  </si>
-  <si>
-    <t>RM400,000 (50% grant; max project spend RM800K)</t>
+    <t>50% of  min project</t>
+  </si>
+  <si>
+    <t>50% grant; max project spend</t>
   </si>
   <si>
     <t>0% — 50% matching grant; recipient contributes 50% of eligible project costs</t>
@@ -1123,20 +1105,10 @@
     <t>Both (SME Corp accepts Islamic financing as co-funding)</t>
   </si>
   <si>
-    <t>Advanced Packaging / OSAT
-Equipment Manufacturing
-Advanced Materials (vendor/supply chain)</t>
-  </si>
-  <si>
     <t>Malaysian SME with SME Status Certification; ≥51% Malaysian-owned; NOT eligible: Main Board PLCs, MNCs, GLCs, large firms</t>
   </si>
   <si>
-    <t>Operating SME; revenue-generating; SCORE rating recommended; &lt;RM50M revenue or &lt;200 employees</t>
-  </si>
-  <si>
-    <t>CapEx (equipment, machinery)
-Talent Acquisition &amp; Upskilling
-Export Promotion / Market Expansion</t>
+    <t>CapEx, Talent Acquisition, Export Promotion, M&amp;A, Go-to-market</t>
   </si>
   <si>
     <t>None; reimbursement-based (spend first, claim back); SME Status &amp; SCORE certification</t>
@@ -1157,6 +1129,9 @@
     <t>MIDA — Pioneer Status (PS)</t>
   </si>
   <si>
+    <t>Tax Incentive</t>
+  </si>
+  <si>
     <t>Tax Incentive — Income Tax Exemption</t>
   </si>
   <si>
@@ -1190,9 +1165,7 @@
     <t>New or expanding manufacturing investment; no minimum revenue; must commit to job creation &amp; capex targets</t>
   </si>
   <si>
-    <t>CapEx (Factory, Equipment — qualifying expenditure)
-R&amp;D &amp; Prototyping
-Promotion of promoted activity</t>
+    <t>R&amp;D &amp; Prototyping, CapEx</t>
   </si>
   <si>
     <t>None (tax incentive); compliance with MIDA-approved promoted activity; annual reporting &amp; auditing</t>
@@ -1228,10 +1201,7 @@
     <t>5–10 years (QCE claim period)</t>
   </si>
   <si>
-    <t>Fabrication / Foundry
-Advanced Packaging / OSAT
-Equipment Manufacturing
-Advanced Materials</t>
+    <t>Fabrication / Foundry, Advanced Packaging / OSAT, Equipment Manufacturing, Advanced Materials</t>
   </si>
   <si>
     <t>Same as Pioneer Status — incorporated in Malaysia; promoted activity; foreign or Malaysian</t>
@@ -1240,9 +1210,6 @@
     <t>Manufacturing investment; alternative to Pioneer Status (cannot claim both simultaneously); capex-heavy projects</t>
   </si>
   <si>
-    <t>CapEx (Machinery, Equipment, Factory, Tooling — qualifying capital expenditure)</t>
-  </si>
-  <si>
     <t>None; MIDA-approved QCE schedule; annual capex auditing and reporting</t>
   </si>
   <si>
@@ -1279,13 +1246,7 @@
     <t>Foreign and Malaysian; incorporated in Malaysia; engaged in NIMP 2030 strategic sectors</t>
   </si>
   <si>
-    <t>Growth-stage to established; must commit to binding outcome targets (headcount, R&amp;D %, exports)</t>
-  </si>
-  <si>
-    <t>CapEx
-R&amp;D &amp; Prototyping
-Talent Acquisition &amp; Upskilling
-Export Promotion</t>
+    <t>R&amp;D &amp; Prototyping, CapEx, Talent Acquisition, Export Promotion, M&amp;A</t>
   </si>
   <si>
     <t>None (tax incentive); binding outcome commitments; MIDA annual tracking &amp; audit</t>
@@ -1321,18 +1282,13 @@
     <t>Minimum 2-year investment hold period</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Advanced Materials
-Equipment Manufacturing (hardware deep-tech)</t>
-  </si>
-  <si>
     <t>SC-certified early-stage startups in 9 eligible technology sectors (hardware &amp; manufacturing tech included); company must hold SC certification</t>
   </si>
   <si>
-    <t>Startup must be SC-certified early-stage; typically pre-revenue to early revenue; &lt;5 years operating</t>
-  </si>
-  <si>
-    <t>Investor-driven (varies per angel round); typically R&amp;D, product development, talent</t>
+    <t>Pre-revenue, Early-stage (Seed–Series A), SME (revenue-generating)</t>
+  </si>
+  <si>
+    <t>R&amp;D &amp; Prototyping, Talent Acquisition</t>
   </si>
   <si>
     <t>None (equity investment); SC certification of startup; minimum 2-year hold</t>
@@ -1371,21 +1327,9 @@
     <t>Both (Islamic financing available via SME Bank-i)</t>
   </si>
   <si>
-    <t>Advanced Packaging / OSAT
-Equipment Manufacturing / Automation
-Advanced Materials (supply chain)</t>
-  </si>
-  <si>
     <t>Malaysian SME; ≥51% Malaysian-owned; registered with SSM; annual sales &lt;RM50M or &lt;200 employees</t>
   </si>
   <si>
-    <t>Operating SME; revenue-generating; &gt;1 year operating history</t>
-  </si>
-  <si>
-    <t>CapEx (Machinery, Equipment, Automation)
-OpEx / Working Capital</t>
-  </si>
-  <si>
     <t>Machinery and equipment; corporate guarantee; personal guarantee for smaller loans</t>
   </si>
   <si>
@@ -1401,6 +1345,9 @@
     <t>EXIM Bank Malaysia (BPMB Group) — Export Credit / Trade Finance</t>
   </si>
   <si>
+    <t>Export Credit</t>
+  </si>
+  <si>
     <t>Export Credit / Trade Finance (Conventional &amp; Islamic)</t>
   </si>
   <si>
@@ -1410,9 +1357,6 @@
     <t>Not fixed (project/deal basis); EXIM Bank part of BPMB Group</t>
   </si>
   <si>
-    <t>RM500 million+</t>
-  </si>
-  <si>
     <t>Export credit rates (below commercial bank rate); typically 3%–6% p.a. (ECA pricing); Islamic: equivalent profit rate</t>
   </si>
   <si>
@@ -1425,20 +1369,13 @@
     <t>Both (Islamic Tawarruq or Murabahah structure available)</t>
   </si>
   <si>
-    <t>Advanced Packaging / OSAT (export of packaged chips)
-Equipment Manufacturing (export of semiconductor equipment)
-All segments (for export receivables)</t>
+    <t>Advanced Packaging / OSAT, Equipment Manufacturing, All Segments</t>
   </si>
   <si>
     <t>Malaysian exporter; incorporated in Malaysia; majority Malaysian-owned preferred</t>
   </si>
   <si>
-    <t>Operating exporter; revenue-generating; export track record or signed export contracts</t>
-  </si>
-  <si>
-    <t>Export Promotion / Market Expansion
-CapEx (for export production capacity)
-Working Capital (export-related)</t>
+    <t>CapEx, OpEx / Working Capital, Export Promotion, Go-to-market</t>
   </si>
   <si>
     <t>Export contracts, letters of credit, receivables assignment; political risk insurance may apply</t>
@@ -1456,6 +1393,9 @@
     <t>SC Malaysia — Equity Crowdfunding (ECF) Platforms</t>
   </si>
   <si>
+    <t>Equity, Crowdfunding</t>
+  </si>
+  <si>
     <t>Equity Crowdfunding (Public Market — Retail Investors)</t>
   </si>
   <si>
@@ -1465,10 +1405,10 @@
     <t>SC-licensed platforms: pitchIN (pitchin.my), Ethis (ethis.co), Ata Plus (ataplus.my)</t>
   </si>
   <si>
-    <t>RM500,000 (minimum typical ECF raise)</t>
-  </si>
-  <si>
-    <t>RM5,000,000 (SC-regulated ECF raise limit per issuer)</t>
+    <t>minimum typical ECF raise</t>
+  </si>
+  <si>
+    <t>SC-regulated ECF raise limit per issuer</t>
   </si>
   <si>
     <t>Equity dilution: typically 10%–30% stake to crowd investors; no interest; investor seeks capital gain</t>
@@ -1480,23 +1420,10 @@
     <t>Ethis = Shariah-compliant ECF; pitchIN &amp; Ata Plus = conventional but may offer Islamic structure</t>
   </si>
   <si>
-    <t>IC Design &amp; Embedded Systems
-Advanced Packaging / OSAT
-Equipment Manufacturing
-Advanced Materials (hardware startups)</t>
-  </si>
-  <si>
     <t>Malaysian Sdn Bhd; ≥51% Malaysian-owned; not a public listed company</t>
   </si>
   <si>
-    <t>Any stage — pre-revenue to early revenue; scalable business model with public-facing pitch</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Prototyping
-CapEx
-OpEx / Working Capital
-Go-to-market
-Talent</t>
+    <t>R&amp;D &amp; Prototyping, CapEx, OpEx / Working Capital, Talent Acquisition, Go-to-market</t>
   </si>
   <si>
     <t>None (equity); SC-registered pitch deck, financial disclosures; platform due diligence</t>
@@ -1514,6 +1441,9 @@
     <t>SC Malaysia — Peer-to-Peer (P2P) Financing Platforms</t>
   </si>
   <si>
+    <t>Crowdfunding</t>
+  </si>
+  <si>
     <t>Debt — P2P / Invoice Financing</t>
   </si>
   <si>
@@ -1523,7 +1453,7 @@
     <t>SC-licensed platforms: Funding Societies, CapBay, B2B Finpal</t>
   </si>
   <si>
-    <t>RM5,000,000 per raise</t>
+    <t>per raise</t>
   </si>
   <si>
     <t>5%–18% p.a. annualised (risk-based pricing by platform); Islamic P2P available (Funding Societies-i, CapBay-i)</t>
@@ -1538,20 +1468,10 @@
     <t>Both (Islamic P2P platforms available: Funding Societies-i, CapBay-i)</t>
   </si>
   <si>
-    <t>Advanced Packaging / OSAT
-Equipment Manufacturing
-Advanced Materials (supply chain SMEs)</t>
-  </si>
-  <si>
     <t>Malaysian SME; ≥51% Malaysian-owned; registered with SSM; revenue-generating</t>
   </si>
   <si>
-    <t>Operating SME; &gt;1 year operating history; must show invoices or contracts for invoice financing</t>
-  </si>
-  <si>
-    <t>OpEx / Working Capital
-Supply chain financing
-Invoice financing (receivables)</t>
+    <t>OpEx / Working Capital</t>
   </si>
   <si>
     <t>Invoice assignment or corporate guarantee; platform-dependent credit scoring</t>
@@ -1807,13 +1727,56 @@
   </si>
   <si>
     <t>Qualifying Capital Expenditure — capex eligible for ITA deduction under MIDA</t>
+  </si>
+  <si>
+    <t>VALID VALUES — FILTER COLUMNS (Comma-separate multiple values per cell)</t>
+  </si>
+  <si>
+    <t>Type of Financing
+(Col C)</t>
+  </si>
+  <si>
+    <t>Target Value Chain
+(Col L)</t>
+  </si>
+  <si>
+    <t>Company Stage / Scale
+(Col N)</t>
+  </si>
+  <si>
+    <t>Permitted Use of Proceeds
+(Col O)</t>
+  </si>
+  <si>
+    <t>Fabrication / Foundry</t>
+  </si>
+  <si>
+    <t>Equipment Manufacturing</t>
+  </si>
+  <si>
+    <t>Talent Acquisition</t>
+  </si>
+  <si>
+    <t>Advanced Materials</t>
+  </si>
+  <si>
+    <t>Export Promotion</t>
+  </si>
+  <si>
+    <t>All Segments</t>
+  </si>
+  <si>
+    <t>M&amp;A</t>
+  </si>
+  <si>
+    <t>Go-to-market</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1826,44 +1789,90 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FFC9A84C"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF111111"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF111111"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF5D4037"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111111"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF111111"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1943,8 +1952,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1982,11 +1996,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF888888"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2024,37 +2062,60 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2356,19 +2417,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S37"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:V37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="22" customWidth="1"/>
@@ -2380,86 +2441,95 @@
     <col min="19" max="19" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="30" customHeight="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-    </row>
-    <row r="2" spans="1:19" ht="15.95" customHeight="1">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+    </row>
+    <row r="2" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-    </row>
-    <row r="3" spans="1:19" ht="18" customHeight="1">
-      <c r="A3" s="21" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+    </row>
+    <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="16" t="s">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="20" t="s">
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="18" t="s">
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="15" t="s">
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="S3" s="23"/>
-    </row>
-    <row r="4" spans="1:19" ht="39.950000000000003" customHeight="1">
+      <c r="V3" s="20"/>
+    </row>
+    <row r="4" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -2469,37 +2539,37 @@
       <c r="C4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="16" t="s">
         <v>17</v>
       </c>
       <c r="K4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="11" t="s">
         <v>19</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="11" t="s">
         <v>21</v>
       </c>
       <c r="O4" s="10" t="s">
@@ -2508,19 +2578,28 @@
       <c r="P4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="R4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="S4" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="T4" s="11" t="s">
         <v>27</v>
+      </c>
+      <c r="U4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="V4" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
+        <v>30</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -2540,213 +2619,239 @@
       <c r="Q5" s="23"/>
       <c r="R5" s="23"/>
       <c r="S5" s="23"/>
-    </row>
-    <row r="6" spans="1:19" ht="57.6">
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="24"/>
+    </row>
+    <row r="6" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="D6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="G6" s="17"/>
+      <c r="H6" s="17" t="s">
         <v>36</v>
       </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17" t="s">
+        <v>37</v>
+      </c>
       <c r="K6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="45.95">
+        <v>46</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="F7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>36</v>
+      <c r="G7" s="18">
+        <v>100000</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="18">
+        <v>5000000</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" ht="34.5">
+      <c r="T7" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="G8" s="17">
+        <v>100000</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="17">
+        <v>5000000</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="L8" s="4" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="O8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="Q8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="R8" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="R8" s="4" t="s">
+      <c r="S8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="S8" s="4" t="s">
+      <c r="T8" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" ht="57.6">
+      <c r="U8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="F9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="18">
+        <v>50000</v>
+      </c>
+      <c r="H9" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="18">
+        <v>5000000</v>
+      </c>
+      <c r="J9" s="18" t="s">
         <v>85</v>
       </c>
       <c r="K9" s="8" t="s">
@@ -2762,142 +2867,161 @@
         <v>89</v>
       </c>
       <c r="O9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P9" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="Q9" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="R9" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="S9" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="R9" s="8" t="s">
+      <c r="T9" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="S9" s="8" t="s">
+      <c r="U9" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" ht="45.95">
+      <c r="V9" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="17">
+        <v>50000</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17">
+        <v>150000</v>
+      </c>
+      <c r="J10" s="17"/>
+      <c r="K10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="4" t="s">
+      <c r="M10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N10" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K10" s="4" t="s">
+      <c r="O10" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="P10" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="Q10" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="R10" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="S10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="T10" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="U10" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="V10" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="S10" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="45.95">
+    </row>
+    <row r="11" spans="1:22" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>6</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="18">
+        <v>500000</v>
+      </c>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18">
+        <v>5000000</v>
+      </c>
+      <c r="J11" s="18"/>
+      <c r="K11" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="M11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="P11" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="Q11" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L11" s="8" t="s">
+      <c r="R11" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="S11" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="T11" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="U11" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="P11" s="8" t="s">
+      <c r="V11" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Q11" s="8" t="s">
+    </row>
+    <row r="12" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="22" t="s">
         <v>122</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="14" t="s">
-        <v>125</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -2917,246 +3041,275 @@
       <c r="Q12" s="23"/>
       <c r="R12" s="23"/>
       <c r="S12" s="23"/>
-    </row>
-    <row r="13" spans="1:19" ht="80.45">
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="24"/>
+    </row>
+    <row r="13" spans="1:22" ht="80.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="G13" s="17">
+        <v>5000000</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17">
+        <v>100000000</v>
+      </c>
+      <c r="J13" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="N13" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="O13" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="P13" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="Q13" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="R13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="S13" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="T13" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="U13" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="P13" s="4" t="s">
+      <c r="V13" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="Q13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="45.95">
+    </row>
+    <row r="14" spans="1:22" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>8</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G14" s="18">
+        <v>1000000</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18">
+        <v>50000000</v>
+      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14" s="9" t="s">
+      <c r="M14" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="N14" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="O14" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="P14" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="Q14" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="R14" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="S14" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="T14" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="U14" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="M14" s="8" t="s">
+      <c r="V14" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="N14" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="S14" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="57.6">
+    </row>
+    <row r="15" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" s="17">
+        <v>50000</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17">
+        <v>3000000</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="M15" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="N15" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="O15" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="P15" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="Q15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R15" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="S15" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="T15" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="U15" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="V15" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="R15" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="45.95">
+    </row>
+    <row r="16" spans="1:22" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>10</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G16" s="18">
+        <v>100000</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18">
+        <v>10000000</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="S16" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E16" s="9" t="s">
+      <c r="T16" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="U16" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="V16" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="H16" s="8" t="s">
+    </row>
+    <row r="17" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="22" t="s">
         <v>180</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="S16" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>190</v>
       </c>
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
@@ -3176,364 +3329,401 @@
       <c r="Q17" s="23"/>
       <c r="R17" s="23"/>
       <c r="S17" s="23"/>
-    </row>
-    <row r="18" spans="1:19" ht="57.6">
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="24"/>
+    </row>
+    <row r="18" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G18" s="17">
+        <v>20000000</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17">
+        <v>200000000</v>
+      </c>
+      <c r="J18" s="17"/>
+      <c r="K18" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S18" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="T18" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="U18" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="V18" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q18" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="R18" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="45.95">
+    </row>
+    <row r="19" spans="1:22" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>12</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>70</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G19" s="18">
+        <v>10000000</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18">
+        <v>200000000</v>
+      </c>
+      <c r="J19" s="18"/>
       <c r="K19" s="8" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>213</v>
+        <v>143</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>214</v>
+        <v>72</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>215</v>
+        <v>58</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>218</v>
+        <v>44</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="S19" s="8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="57.6">
+        <v>200</v>
+      </c>
+      <c r="T19" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="U19" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="V19" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>13</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>228</v>
+        <v>182</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17" t="s">
+        <v>208</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>233</v>
+        <v>59</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="45.95">
+        <v>216</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>14</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="D21" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D21" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>199</v>
+      <c r="E21" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="G21" s="18">
+        <v>500000</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="I21" s="18">
+        <v>20000000</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>225</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>54</v>
+        <v>226</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>247</v>
+        <v>58</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>248</v>
+        <v>101</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="S21" s="8" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="57.6">
+        <v>231</v>
+      </c>
+      <c r="T21" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="U21" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="V21" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>15</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>70</v>
+        <v>221</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17" t="s">
+        <v>240</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>117</v>
+        <v>242</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>262</v>
+        <v>72</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>264</v>
+        <v>101</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="45.95">
+        <v>246</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>16</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>199</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="G23" s="18">
+        <v>20000000</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18">
+        <v>100000000</v>
+      </c>
+      <c r="J23" s="18"/>
       <c r="K23" s="8" t="s">
-        <v>54</v>
+        <v>253</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>276</v>
+        <v>188</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>277</v>
+        <v>58</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>281</v>
+        <v>45</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="14" t="s">
-        <v>283</v>
+        <v>258</v>
+      </c>
+      <c r="T23" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="U23" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="V23" s="8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="22" t="s">
+        <v>262</v>
       </c>
       <c r="B24" s="23"/>
       <c r="C24" s="23"/>
@@ -3553,187 +3743,215 @@
       <c r="Q24" s="23"/>
       <c r="R24" s="23"/>
       <c r="S24" s="23"/>
-    </row>
-    <row r="25" spans="1:19" ht="69">
+      <c r="T24" s="23"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="24"/>
+    </row>
+    <row r="25" spans="1:22" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>17</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>70</v>
+        <v>264</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="I25" s="17">
+        <v>500000</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>269</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>54</v>
+        <v>270</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>293</v>
+        <v>72</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>294</v>
+        <v>58</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>295</v>
+        <v>101</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>298</v>
+        <v>117</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="69">
+        <v>274</v>
+      </c>
+      <c r="T25" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>18</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>308</v>
+        <v>32</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="G26" s="18">
+        <v>250000</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="I26" s="18">
+        <v>15000000</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>283</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>54</v>
+        <v>284</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>311</v>
+        <v>58</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="S26" s="8" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="57.6">
+        <v>290</v>
+      </c>
+      <c r="T26" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="U26" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="V26" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>19</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>70</v>
+        <v>32</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="G27" s="17">
+        <v>50000</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="I27" s="17">
+        <v>400000</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>299</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>327</v>
+        <v>72</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>329</v>
+        <v>162</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>330</v>
+        <v>303</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>331</v>
+        <v>61</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="14" t="s">
-        <v>334</v>
+        <v>305</v>
+      </c>
+      <c r="T27" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="U27" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="V27" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="22" t="s">
+        <v>309</v>
       </c>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
@@ -3753,246 +3971,269 @@
       <c r="Q28" s="23"/>
       <c r="R28" s="23"/>
       <c r="S28" s="23"/>
-    </row>
-    <row r="29" spans="1:19" ht="57.6">
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="24"/>
+    </row>
+    <row r="29" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>20</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>343</v>
+        <v>311</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18" t="s">
+        <v>316</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>344</v>
+        <v>317</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>38</v>
+        <v>318</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>347</v>
+        <v>42</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="S29" s="8" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="69">
+        <v>324</v>
+      </c>
+      <c r="T29" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="U29" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="V29" s="8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>21</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="D30" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q30" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="O30" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="P30" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q30" s="4" t="s">
-        <v>364</v>
-      </c>
       <c r="R30" s="4" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="57.6">
+        <v>338</v>
+      </c>
+      <c r="T30" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="U30" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="V30" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>22</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>70</v>
+        <v>311</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18" t="s">
+        <v>346</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>54</v>
+        <v>347</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>135</v>
+        <v>348</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>374</v>
+        <v>72</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>375</v>
+        <v>58</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>376</v>
+        <v>133</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>378</v>
+        <v>44</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="S31" s="8" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="69">
+        <v>351</v>
+      </c>
+      <c r="T31" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="U31" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="V31" s="8" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>23</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>70</v>
+        <v>311</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17" t="s">
+        <v>359</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>54</v>
+        <v>360</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>389</v>
+        <v>72</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>390</v>
+        <v>58</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>391</v>
+        <v>101</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="14" t="s">
-        <v>396</v>
+        <v>365</v>
+      </c>
+      <c r="T32" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="U32" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="V32" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="22" t="s">
+        <v>369</v>
       </c>
       <c r="B33" s="23"/>
       <c r="C33" s="23"/>
@@ -4012,607 +4253,637 @@
       <c r="Q33" s="23"/>
       <c r="R33" s="23"/>
       <c r="S33" s="23"/>
-    </row>
-    <row r="34" spans="1:19" ht="57.6">
+      <c r="T33" s="23"/>
+      <c r="U33" s="23"/>
+      <c r="V33" s="24"/>
+    </row>
+    <row r="34" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>24</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>402</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="G34" s="18">
+        <v>50000</v>
+      </c>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18">
+        <v>20000000</v>
+      </c>
+      <c r="J34" s="18"/>
       <c r="K34" s="8" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>404</v>
+        <v>159</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="N34" s="8" t="s">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="O34" s="8" t="s">
-        <v>407</v>
+        <v>162</v>
       </c>
       <c r="P34" s="8" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="Q34" s="8" t="s">
-        <v>409</v>
+        <v>61</v>
       </c>
       <c r="R34" s="8" t="s">
-        <v>410</v>
+        <v>148</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="69">
+        <v>378</v>
+      </c>
+      <c r="T34" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="U34" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="V34" s="8" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>25</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>419</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="G35" s="17">
+        <v>1000000</v>
+      </c>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17">
+        <v>500000000</v>
+      </c>
+      <c r="J35" s="17"/>
       <c r="K35" s="4" t="s">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>426</v>
+        <v>61</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>427</v>
+        <v>393</v>
       </c>
       <c r="S35" s="4" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="69">
+        <v>394</v>
+      </c>
+      <c r="T35" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="U35" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="V35" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>26</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>199</v>
+        <v>399</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G36" s="18">
+        <v>500000</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="I36" s="18">
+        <v>5000000</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>404</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>438</v>
+        <v>406</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>439</v>
+        <v>188</v>
       </c>
       <c r="N36" s="8" t="s">
-        <v>440</v>
+        <v>407</v>
       </c>
       <c r="O36" s="8" t="s">
-        <v>441</v>
+        <v>255</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>442</v>
+        <v>408</v>
       </c>
       <c r="Q36" s="8" t="s">
-        <v>443</v>
+        <v>273</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>444</v>
+        <v>409</v>
       </c>
       <c r="S36" s="8" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="57.6">
+        <v>410</v>
+      </c>
+      <c r="T36" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="U36" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="V36" s="8" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>27</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>453</v>
+        <v>415</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G37" s="17">
+        <v>50000</v>
+      </c>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17">
+        <v>5000000</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>419</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>454</v>
+        <v>420</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>455</v>
+        <v>421</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>456</v>
+        <v>422</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>458</v>
+        <v>162</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>459</v>
+        <v>424</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>460</v>
+        <v>61</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="S37" s="4" t="s">
-        <v>462</v>
+        <v>426</v>
+      </c>
+      <c r="T37" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="U37" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="V37" s="4" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A33:S33"/>
-    <mergeCell ref="A5:S5"/>
-    <mergeCell ref="A28:S28"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A17:S17"/>
-    <mergeCell ref="A24:S24"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="A12:S12"/>
-    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="A33:V33"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A5:V5"/>
+    <mergeCell ref="A17:V17"/>
+    <mergeCell ref="A12:V12"/>
     <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A24:V24"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="A28:V28"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="K3:N3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21.95" customHeight="1">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" s="20"/>
+    </row>
+    <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
+        <v>431</v>
+      </c>
+      <c r="B2" s="20"/>
+    </row>
+    <row r="3" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="31" t="s">
+        <v>451</v>
+      </c>
+      <c r="B13" s="20"/>
+    </row>
+    <row r="14" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="31" t="s">
+        <v>462</v>
+      </c>
+      <c r="B19" s="20"/>
+    </row>
+    <row r="20" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="B1" s="23"/>
-    </row>
-    <row r="2" spans="1:2" ht="21.95" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="B20" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="B2" s="23"/>
-    </row>
-    <row r="3" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="21" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A4" s="7" t="s">
+      <c r="B21" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="B4" s="8" t="s">
+    </row>
+    <row r="22" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="B22" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="B5" s="4" t="s">
+    </row>
+    <row r="23" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="B23" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="B6" s="8" t="s">
+    </row>
+    <row r="24" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A7" s="3" t="s">
+      <c r="B24" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="B7" s="4" t="s">
+    </row>
+    <row r="25" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="B25" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="B8" s="8" t="s">
+    </row>
+    <row r="26" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A9" s="3" t="s">
+      <c r="B26" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A10" s="7" t="s">
+      <c r="B27" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="B10" s="8" t="s">
+    </row>
+    <row r="28" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="B28" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="B11" s="4" t="s">
+    </row>
+    <row r="29" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A12" s="7" t="s">
+      <c r="B29" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="B12" s="8" t="s">
+    </row>
+    <row r="30" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="21.95" customHeight="1">
-      <c r="A13" s="22" t="s">
+      <c r="B30" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="B13" s="23"/>
-    </row>
-    <row r="14" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A14" s="7" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B31" s="4" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A15" s="3" t="s">
+    <row r="32" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B32" s="8" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A16" s="7" t="s">
+    <row r="33" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B33" s="4" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A17" s="3" t="s">
+    <row r="34" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B34" s="8" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A18" s="7" t="s">
+    <row r="35" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B35" s="4" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="21.95" customHeight="1">
-      <c r="A19" s="22" t="s">
+    <row r="36" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="B19" s="23"/>
-    </row>
-    <row r="20" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A20" s="7" t="s">
+      <c r="B36" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="B20" s="8" t="s">
+    </row>
+    <row r="37" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A21" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="B21" s="4" t="s">
+    </row>
+    <row r="38" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="7" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A22" s="7" t="s">
+      <c r="B38" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="B22" s="8" t="s">
+    </row>
+    <row r="39" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A23" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="B23" s="4" t="s">
+    </row>
+    <row r="40" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="7" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A24" s="7" t="s">
+      <c r="B40" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="B24" s="8" t="s">
+    </row>
+    <row r="41" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A25" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="B25" s="4" t="s">
+    </row>
+    <row r="42" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="7" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A26" s="7" t="s">
+      <c r="B42" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="B26" s="8" t="s">
+    </row>
+    <row r="43" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A27" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>510</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A28" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A30" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A32" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A33" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A34" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A36" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A38" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A39" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A40" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A41" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A42" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="38.1" customHeight="1">
-      <c r="A43" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -4624,4 +4895,136 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="4" width="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+    </row>
+    <row r="2" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>517</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>445</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>